--- a/data/processed/hungarian_websites.xlsx
+++ b/data/processed/hungarian_websites.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEDCB7B7-CE8E-0546-93AD-6977D6ADE99F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A30AB3-C276-1F49-9B8F-CAE146943BD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="800" yWindow="1280" windowWidth="32240" windowHeight="18520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3239,7 +3239,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3254,12 +3254,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -3295,7 +3289,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3945,6 +3939,31 @@
             <v>travelo.hu</v>
           </cell>
         </row>
+        <row r="125">
+          <cell r="A125" t="str">
+            <v>lebelier.hu</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="A126" t="str">
+            <v>m4sportelo.hu</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="A127" t="str">
+            <v>zoldlepes.hu</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="A128" t="str">
+            <v>kreativ.hu</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="A129" t="str">
+            <v>lovasok.hu</v>
+          </cell>
+        </row>
       </sheetData>
     </sheetDataSet>
   </externalBook>
@@ -20918,10 +20937,6 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -23974,7 +23989,7 @@
       </c>
       <c r="B220" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A220)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
@@ -24271,7 +24286,7 @@
       </c>
       <c r="B253" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A253)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.2">
@@ -25720,7 +25735,7 @@
       </c>
       <c r="B414" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A414)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.2">
@@ -28015,7 +28030,7 @@
       </c>
       <c r="B669" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A669)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.2">
@@ -28024,7 +28039,7 @@
       </c>
       <c r="B670" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A670)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.2">

--- a/data/processed/hungarian_websites.xlsx
+++ b/data/processed/hungarian_websites.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A30AB3-C276-1F49-9B8F-CAE146943BD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA773BD9-2825-9244-A4F2-197E56ED55AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="800" yWindow="1280" windowWidth="32240" windowHeight="18520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hungarian_websites" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="1058">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="1070">
   <si>
     <t>videa.hu</t>
   </si>
@@ -3233,6 +3233,42 @@
   </si>
   <si>
     <t>https://www.nosalty.hu/impresszum</t>
+  </si>
+  <si>
+    <t>https://www.origo.hu/impresszum</t>
+  </si>
+  <si>
+    <t>ATW INTERNET</t>
+  </si>
+  <si>
+    <t>https://atw.hu/</t>
+  </si>
+  <si>
+    <t>Online Comparison Shopping</t>
+  </si>
+  <si>
+    <t>https://www.arukereso.hu/static/elerhetosegeink.html</t>
+  </si>
+  <si>
+    <t>https://www.e-cegjegyzek.hu/?cegadatlap/0109186759/Cegbetekintes</t>
+  </si>
+  <si>
+    <t>https://www.e-cegjegyzek.hu/?cegadatlap/0109736956/Cegbetekintes</t>
+  </si>
+  <si>
+    <t>https://www.blikk.hu/katalogus/impresszum/rj58q0w</t>
+  </si>
+  <si>
+    <t>https://accounts.freemail.hu/a/login</t>
+  </si>
+  <si>
+    <t>https://www.e-cegjegyzek.hu/?cegadatlap/0109404379/Cegbetekintes</t>
+  </si>
+  <si>
+    <t>https://www.nemzetisport.hu/impresszum</t>
+  </si>
+  <si>
+    <t>N.S. MÉDIA ÉS VAGYONKEZELŐ</t>
   </si>
 </sst>
 </file>
@@ -21278,7 +21314,7 @@
     <col min="1" max="1" width="24.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="71" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23.5" bestFit="1" customWidth="1"/>
@@ -21548,7 +21584,7 @@
       <c r="F5" s="2" t="s">
         <v>1031</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="3">
         <v>62.2</v>
       </c>
       <c r="I5" t="str">
@@ -22146,6 +22182,58 @@
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A15)&gt;0,"Igen","Nem")</f>
         <v>Nem</v>
       </c>
+      <c r="C15" s="1">
+        <v>45869</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="H15">
+        <v>58.12</v>
+      </c>
+      <c r="I15" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H15,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$H:$H)</f>
+        <v>Napilapkiadás</v>
+      </c>
+      <c r="J15" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H15,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$E:$E)</f>
+        <v>58.1</v>
+      </c>
+      <c r="K15" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H15,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$F:$F)</f>
+        <v>Könyv-, napilapkiadás, egyéb kiadói tevékenység (kivéve: szoftverkiadás)</v>
+      </c>
+      <c r="L15" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H15,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$C:$C)</f>
+        <v>58</v>
+      </c>
+      <c r="M15" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H15,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$D:$D)</f>
+        <v>Kiadói tevékenység</v>
+      </c>
+      <c r="N15" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H15,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$A:$A)</f>
+        <v>J</v>
+      </c>
+      <c r="O15" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H15,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$B:$B)</f>
+        <v>KIADÓI TEVÉKENYSÉG, MŰSORSZOLGÁLTATÁS, TARTALOMSZOLGÁLTATÁS ÉS -TERJESZTÉS</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="Q15">
+        <v>70279652000</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>1027</v>
+      </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -22155,8 +22243,60 @@
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A16)&gt;0,"Igen","Nem")</f>
         <v>Nem</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C16" s="1">
+        <v>45869</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H16" s="3">
+        <v>62.2</v>
+      </c>
+      <c r="I16" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H16,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$H:$H)</f>
+        <v>Információtechnológiai szaktanácsadás és számítástechnikai eszközök, rendszerek üzemeltetése</v>
+      </c>
+      <c r="J16" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H16,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$E:$E)</f>
+        <v>62.2</v>
+      </c>
+      <c r="K16" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H16,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$F:$F)</f>
+        <v>Információtechnológiai szaktanácsadás és számítástechnikai eszközök, rendszerek üzemeltetése</v>
+      </c>
+      <c r="L16" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H16,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$C:$C)</f>
+        <v>62</v>
+      </c>
+      <c r="M16" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H16,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$D:$D)</f>
+        <v>Információtechnológiai szolgáltatás</v>
+      </c>
+      <c r="N16" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H16,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$A:$A)</f>
+        <v>K</v>
+      </c>
+      <c r="O16" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H16,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$B:$B)</f>
+        <v>TÁVKÖZLÉS, SZÁMÍTÓGÉPES PROGRAMOZÁS, INFORMÁCIÓTECHNOLÓGIAI SZAKTANÁCSADÁS, SZÁMÍTÁSTECHNIKAI INFRASTRUKTÚRA ÉS EGYÉB INFORMÁCIÓS SZOLGÁLTATÁSOK</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="Q16">
+        <v>374795000</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -22165,7 +22305,7 @@
         <v>Nem</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -22173,8 +22313,60 @@
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A18)&gt;0,"Igen","Nem")</f>
         <v>Nem</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C18" s="1">
+        <v>45869</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H18">
+        <v>63.91</v>
+      </c>
+      <c r="I18" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H18,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$H:$H)</f>
+        <v>Internetes keresőportállal kapcsolatos tevékenységek</v>
+      </c>
+      <c r="J18" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H18,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$E:$E)</f>
+        <v>63.9</v>
+      </c>
+      <c r="K18" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H18,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$F:$F)</f>
+        <v>Internetes keresőportállal kapcsolatos tevékenységek és egyéb információs szolgáltatás</v>
+      </c>
+      <c r="L18" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H18,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$C:$C)</f>
+        <v>63</v>
+      </c>
+      <c r="M18" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H18,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$D:$D)</f>
+        <v>Számítástechnikai infrastruktúra, adatfeldolgozás, tárhelyszolgáltatás és egyéb információs szolgáltatási tevékenységek</v>
+      </c>
+      <c r="N18" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H18,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$A:$A)</f>
+        <v>K</v>
+      </c>
+      <c r="O18" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H18,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$B:$B)</f>
+        <v>TÁVKÖZLÉS, SZÁMÍTÓGÉPES PROGRAMOZÁS, INFORMÁCIÓTECHNOLÓGIAI SZAKTANÁCSADÁS, SZÁMÍTÁSTECHNIKAI INFRASTRUKTÚRA ÉS EGYÉB INFORMÁCIÓS SZOLGÁLTATÁSOK</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="Q18">
+        <v>9219370000</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -22182,8 +22374,60 @@
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A19)&gt;0,"Igen","Nem")</f>
         <v>Nem</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C19" s="1">
+        <v>45869</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="H19">
+        <v>58.13</v>
+      </c>
+      <c r="I19" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H19,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$H:$H)</f>
+        <v>Folyóirat, időszaki kiadvány kiadása</v>
+      </c>
+      <c r="J19" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H19,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$E:$E)</f>
+        <v>58.1</v>
+      </c>
+      <c r="K19" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H19,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$F:$F)</f>
+        <v>Könyv-, napilapkiadás, egyéb kiadói tevékenység (kivéve: szoftverkiadás)</v>
+      </c>
+      <c r="L19" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H19,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$C:$C)</f>
+        <v>58</v>
+      </c>
+      <c r="M19" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H19,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$D:$D)</f>
+        <v>Kiadói tevékenység</v>
+      </c>
+      <c r="N19" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H19,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$A:$A)</f>
+        <v>J</v>
+      </c>
+      <c r="O19" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H19,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$B:$B)</f>
+        <v>KIADÓI TEVÉKENYSÉG, MŰSORSZOLGÁLTATÁS, TARTALOMSZOLGÁLTATÁS ÉS -TERJESZTÉS</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="Q19">
+        <v>12119082000</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -22191,8 +22435,60 @@
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A20)&gt;0,"Igen","Nem")</f>
         <v>Nem</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C20" s="1">
+        <v>45869</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="H20">
+        <v>58.12</v>
+      </c>
+      <c r="I20" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H20,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$H:$H)</f>
+        <v>Napilapkiadás</v>
+      </c>
+      <c r="J20" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H20,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$E:$E)</f>
+        <v>58.1</v>
+      </c>
+      <c r="K20" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H20,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$F:$F)</f>
+        <v>Könyv-, napilapkiadás, egyéb kiadói tevékenység (kivéve: szoftverkiadás)</v>
+      </c>
+      <c r="L20" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H20,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$C:$C)</f>
+        <v>58</v>
+      </c>
+      <c r="M20" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H20,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$D:$D)</f>
+        <v>Kiadói tevékenység</v>
+      </c>
+      <c r="N20" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H20,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$A:$A)</f>
+        <v>J</v>
+      </c>
+      <c r="O20" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H20,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$B:$B)</f>
+        <v>KIADÓI TEVÉKENYSÉG, MŰSORSZOLGÁLTATÁS, TARTALOMSZOLGÁLTATÁS ÉS -TERJESZTÉS</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="Q20">
+        <v>70279652000</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -22200,8 +22496,60 @@
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A21)&gt;0,"Igen","Nem")</f>
         <v>Nem</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C21" s="1">
+        <v>45869</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H21">
+        <v>58.12</v>
+      </c>
+      <c r="I21" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H21,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$H:$H)</f>
+        <v>Napilapkiadás</v>
+      </c>
+      <c r="J21" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H21,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$E:$E)</f>
+        <v>58.1</v>
+      </c>
+      <c r="K21" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H21,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$F:$F)</f>
+        <v>Könyv-, napilapkiadás, egyéb kiadói tevékenység (kivéve: szoftverkiadás)</v>
+      </c>
+      <c r="L21" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H21,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$C:$C)</f>
+        <v>58</v>
+      </c>
+      <c r="M21" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H21,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$D:$D)</f>
+        <v>Kiadói tevékenység</v>
+      </c>
+      <c r="N21" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H21,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$A:$A)</f>
+        <v>J</v>
+      </c>
+      <c r="O21" t="str">
+        <f>_xlfn.XLOOKUP(TEXT($H21,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$B:$B)</f>
+        <v>KIADÓI TEVÉKENYSÉG, MŰSORSZOLGÁLTATÁS, TARTALOMSZOLGÁLTATÁS ÉS -TERJESZTÉS</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="Q21">
+        <v>1983293000</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -22209,8 +22557,36 @@
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A22)&gt;0,"Igen","Nem")</f>
         <v>Nem</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="I22" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H22,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$H:$H)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J22" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H22,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$E:$E)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K22" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H22,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$F:$F)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L22" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H22,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$C:$C)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M22" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H22,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$D:$D)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N22" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H22,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$A:$A)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="O22" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H22,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$B:$B)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -22218,8 +22594,36 @@
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A23)&gt;0,"Igen","Nem")</f>
         <v>Nem</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="I23" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H23,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$H:$H)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J23" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H23,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$E:$E)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K23" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H23,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$F:$F)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L23" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H23,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$C:$C)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M23" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H23,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$D:$D)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N23" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H23,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$A:$A)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="O23" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H23,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$B:$B)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -22227,8 +22631,36 @@
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A24)&gt;0,"Igen","Nem")</f>
         <v>Nem</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="I24" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H24,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$H:$H)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J24" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H24,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$E:$E)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K24" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H24,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$F:$F)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L24" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H24,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$C:$C)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M24" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H24,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$D:$D)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N24" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H24,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$A:$A)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="O24" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H24,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$B:$B)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -22236,8 +22668,36 @@
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A25)&gt;0,"Igen","Nem")</f>
         <v>Nem</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="I25" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H25,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$H:$H)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J25" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H25,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$E:$E)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K25" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H25,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$F:$F)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L25" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H25,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$C:$C)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M25" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H25,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$D:$D)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N25" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H25,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$A:$A)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="O25" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H25,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$B:$B)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -22245,8 +22705,36 @@
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A26)&gt;0,"Igen","Nem")</f>
         <v>Nem</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="I26" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H26,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$H:$H)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J26" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H26,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$E:$E)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K26" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H26,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$F:$F)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L26" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H26,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$C:$C)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M26" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H26,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$D:$D)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N26" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H26,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$A:$A)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="O26" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H26,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$B:$B)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -22254,8 +22742,36 @@
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A27)&gt;0,"Igen","Nem")</f>
         <v>Nem</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="I27" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H27,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$H:$H)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J27" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H27,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$E:$E)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K27" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H27,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$F:$F)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L27" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H27,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$C:$C)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M27" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H27,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$D:$D)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N27" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H27,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$A:$A)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="O27" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H27,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$B:$B)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -22263,8 +22779,36 @@
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A28)&gt;0,"Igen","Nem")</f>
         <v>Nem</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="I28" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H28,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$H:$H)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J28" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H28,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$E:$E)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K28" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H28,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$F:$F)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L28" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H28,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$C:$C)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M28" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H28,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$D:$D)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N28" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H28,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$A:$A)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="O28" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H28,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$B:$B)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -22272,8 +22816,36 @@
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A29)&gt;0,"Igen","Nem")</f>
         <v>Nem</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="I29" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H29,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$H:$H)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J29" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H29,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$E:$E)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K29" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H29,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$F:$F)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L29" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H29,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$C:$C)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M29" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H29,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$D:$D)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N29" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H29,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$A:$A)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="O29" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H29,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$B:$B)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -22281,8 +22853,36 @@
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A30)&gt;0,"Igen","Nem")</f>
         <v>Nem</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="I30" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H30,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$H:$H)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J30" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H30,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$E:$E)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K30" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H30,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$F:$F)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L30" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H30,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$C:$C)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M30" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H30,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$D:$D)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N30" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H30,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$A:$A)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="O30" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H30,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$B:$B)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -22290,8 +22890,36 @@
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A31)&gt;0,"Igen","Nem")</f>
         <v>Nem</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="I31" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H31,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$H:$H)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J31" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H31,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$E:$E)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K31" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H31,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$F:$F)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L31" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H31,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$C:$C)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M31" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H31,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$D:$D)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N31" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H31,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$A:$A)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="O31" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H31,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$B:$B)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -22299,8 +22927,36 @@
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A32)&gt;0,"Igen","Nem")</f>
         <v>Nem</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="I32" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H32,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$H:$H)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J32" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H32,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$E:$E)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K32" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H32,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$F:$F)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L32" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H32,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$C:$C)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M32" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H32,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$D:$D)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N32" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H32,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$A:$A)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="O32" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H32,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$B:$B)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -22308,8 +22964,36 @@
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A33)&gt;0,"Igen","Nem")</f>
         <v>Nem</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="I33" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H33,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$H:$H)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J33" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H33,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$E:$E)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K33" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H33,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$F:$F)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L33" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H33,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$C:$C)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M33" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H33,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$D:$D)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N33" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H33,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$A:$A)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="O33" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H33,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$B:$B)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -22317,8 +23001,36 @@
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A34)&gt;0,"Igen","Nem")</f>
         <v>Nem</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="I34" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H34,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$H:$H)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J34" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H34,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$E:$E)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K34" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H34,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$F:$F)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L34" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H34,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$C:$C)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M34" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H34,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$D:$D)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N34" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H34,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$A:$A)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="O34" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H34,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$B:$B)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -22326,8 +23038,36 @@
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A35)&gt;0,"Igen","Nem")</f>
         <v>Nem</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="I35" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H35,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$H:$H)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J35" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H35,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$E:$E)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K35" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H35,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$F:$F)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L35" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H35,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$C:$C)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M35" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H35,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$D:$D)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N35" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H35,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$A:$A)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="O35" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H35,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$B:$B)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -22335,8 +23075,36 @@
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A36)&gt;0,"Igen","Nem")</f>
         <v>Nem</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="I36" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H36,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$H:$H)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J36" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H36,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$E:$E)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K36" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H36,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$F:$F)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L36" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H36,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$C:$C)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M36" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H36,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$D:$D)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N36" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H36,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$A:$A)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="O36" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H36,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$B:$B)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -22344,8 +23112,36 @@
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A37)&gt;0,"Igen","Nem")</f>
         <v>Nem</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="I37" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H37,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$H:$H)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J37" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H37,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$E:$E)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K37" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H37,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$F:$F)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L37" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H37,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$C:$C)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M37" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H37,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$D:$D)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N37" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H37,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$A:$A)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="O37" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H37,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$B:$B)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -22353,8 +23149,36 @@
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A38)&gt;0,"Igen","Nem")</f>
         <v>Nem</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="I38" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H38,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$H:$H)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J38" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H38,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$E:$E)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K38" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H38,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$F:$F)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L38" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H38,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$C:$C)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M38" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H38,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$D:$D)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N38" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H38,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$A:$A)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="O38" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H38,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$B:$B)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -22362,8 +23186,36 @@
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A39)&gt;0,"Igen","Nem")</f>
         <v>Nem</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="I39" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H39,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$H:$H)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J39" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H39,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$E:$E)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K39" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H39,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$F:$F)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L39" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H39,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$C:$C)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M39" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H39,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$D:$D)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N39" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H39,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$A:$A)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="O39" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H39,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$B:$B)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -22371,8 +23223,36 @@
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A40)&gt;0,"Igen","Nem")</f>
         <v>Nem</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="I40" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H40,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$H:$H)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J40" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H40,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$E:$E)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K40" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H40,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$F:$F)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L40" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H40,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$C:$C)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M40" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H40,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$D:$D)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N40" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H40,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$A:$A)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="O40" t="e">
+        <f>_xlfn.XLOOKUP(TEXT($H40,"0.00"),'[2]TEÁOR''25 struktúra'!$G:$G,'[2]TEÁOR''25 struktúra'!$B:$B)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -22381,7 +23261,7 @@
         <v>Nem</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -22390,7 +23270,7 @@
         <v>Nem</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -22399,7 +23279,7 @@
         <v>Nem</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -22408,7 +23288,7 @@
         <v>Nem</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -22417,7 +23297,7 @@
         <v>Nem</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -22426,7 +23306,7 @@
         <v>Nem</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -22435,7 +23315,7 @@
         <v>Nem</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -31061,9 +31941,27 @@
     <hyperlink ref="F14" r:id="rId36" xr:uid="{A310F288-91B1-EC45-AB83-DCE99CB50D63}"/>
     <hyperlink ref="P14" r:id="rId37" xr:uid="{FE400004-0B52-BE44-8B28-442806899C9E}"/>
     <hyperlink ref="R14" r:id="rId38" xr:uid="{2C98EBEF-136D-5F4A-AA61-DDC8CD3D4FA8}"/>
+    <hyperlink ref="F15" r:id="rId39" xr:uid="{7758C9B4-91C5-1C40-BA69-839CE85AB368}"/>
+    <hyperlink ref="P15" r:id="rId40" xr:uid="{4C12D2B0-2062-454E-AF28-5861BE74F79B}"/>
+    <hyperlink ref="R15" r:id="rId41" xr:uid="{50D0CCB7-87AD-E649-A917-21FC0EB4C88B}"/>
+    <hyperlink ref="F16" r:id="rId42" xr:uid="{30E5B90F-8CAD-E94C-9D61-F7E1E3FA5251}"/>
+    <hyperlink ref="F18" r:id="rId43" xr:uid="{991C4F1D-7F2B-9F4D-AE26-F69937420FF2}"/>
+    <hyperlink ref="P18" r:id="rId44" xr:uid="{CFFB71BE-57EA-0A42-9D30-A42037B0338A}"/>
+    <hyperlink ref="R18" r:id="rId45" xr:uid="{F3953AD5-E21A-4D46-9094-D1F1C4DA5351}"/>
+    <hyperlink ref="P16" r:id="rId46" xr:uid="{45665F61-182D-6349-B0CD-550D4C1FE31D}"/>
+    <hyperlink ref="R16" r:id="rId47" xr:uid="{2950B282-402D-084D-A159-117C7F1BE332}"/>
+    <hyperlink ref="F19" r:id="rId48" xr:uid="{AFEA1BF5-402C-7846-A5D1-A8D7B751D2B1}"/>
+    <hyperlink ref="P19" r:id="rId49" xr:uid="{5A93AF37-B18A-504D-9FB8-4F2070072A89}"/>
+    <hyperlink ref="R19" r:id="rId50" xr:uid="{148C8645-838D-5D4B-BD98-F35C7D1A9A59}"/>
+    <hyperlink ref="F20" r:id="rId51" xr:uid="{595C19E2-683E-D14E-8D9D-3182F851A3F6}"/>
+    <hyperlink ref="P20" r:id="rId52" xr:uid="{23A420AE-8606-2645-BFCE-ACF341B0FB78}"/>
+    <hyperlink ref="R20" r:id="rId53" xr:uid="{731A3546-9C9C-FA42-962C-F4CF5B84E504}"/>
+    <hyperlink ref="R21" r:id="rId54" xr:uid="{64416061-AA6B-6543-8658-C5FE0078E18F}"/>
+    <hyperlink ref="P21" r:id="rId55" xr:uid="{9F2653AB-EB67-ED43-AEA1-E43C6C2E5CDE}"/>
+    <hyperlink ref="F21" r:id="rId56" xr:uid="{E45DE812-3C71-8A45-B52E-F2A5ED5AD139}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-  <legacyDrawing r:id="rId39"/>
+  <legacyDrawing r:id="rId57"/>
 </worksheet>
 </file>
--- a/data/processed/hungarian_websites.xlsx
+++ b/data/processed/hungarian_websites.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA773BD9-2825-9244-A4F2-197E56ED55AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71537F2-6BDD-F040-8CAB-01799F167DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3998,6 +3998,36 @@
         <row r="129">
           <cell r="A129" t="str">
             <v>lovasok.hu</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="A130" t="str">
+            <v>greenaqua.hu</v>
+          </cell>
+        </row>
+        <row r="131">
+          <cell r="A131" t="str">
+            <v>gazdabolt.hu</v>
+          </cell>
+        </row>
+        <row r="132">
+          <cell r="A132" t="str">
+            <v>okosdoboz.hu</v>
+          </cell>
+        </row>
+        <row r="133">
+          <cell r="A133" t="str">
+            <v>polomania.hu</v>
+          </cell>
+        </row>
+        <row r="134">
+          <cell r="A134" t="str">
+            <v>molfehervarfc.hu</v>
+          </cell>
+        </row>
+        <row r="135">
+          <cell r="A135" t="str">
+            <v>kozelben.hu</v>
           </cell>
         </row>
       </sheetData>
@@ -29072,7 +29102,7 @@
       </c>
       <c r="B687" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A687)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.2">
@@ -30476,7 +30506,7 @@
       </c>
       <c r="B843" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A843)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="844" spans="1:2" x14ac:dyDescent="0.2">
@@ -31061,7 +31091,7 @@
       </c>
       <c r="B908" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A908)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="909" spans="1:2" x14ac:dyDescent="0.2">
@@ -31493,7 +31523,7 @@
       </c>
       <c r="B956" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A956)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="957" spans="1:2" x14ac:dyDescent="0.2">
@@ -31628,7 +31658,7 @@
       </c>
       <c r="B971" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A971)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="972" spans="1:2" x14ac:dyDescent="0.2">
@@ -31871,7 +31901,7 @@
       </c>
       <c r="B998" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A998)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="999" spans="1:2" x14ac:dyDescent="0.2">

--- a/data/processed/hungarian_websites.xlsx
+++ b/data/processed/hungarian_websites.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71537F2-6BDD-F040-8CAB-01799F167DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4931BDE0-1946-D24F-B4EA-9013BD5C36F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4028,6 +4028,16 @@
         <row r="135">
           <cell r="A135" t="str">
             <v>kozelben.hu</v>
+          </cell>
+        </row>
+        <row r="136">
+          <cell r="A136" t="str">
+            <v>meduzaingatlan.hu</v>
+          </cell>
+        </row>
+        <row r="137">
+          <cell r="A137" t="str">
+            <v>bpbutor.hu</v>
           </cell>
         </row>
       </sheetData>
@@ -26762,7 +26772,7 @@
       </c>
       <c r="B427" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A427)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.2">
@@ -27203,7 +27213,7 @@
       </c>
       <c r="B476" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A476)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.2">

--- a/data/processed/hungarian_websites.xlsx
+++ b/data/processed/hungarian_websites.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4931BDE0-1946-D24F-B4EA-9013BD5C36F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A14F6D-BA06-314B-9700-981972499985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4038,6 +4038,11 @@
         <row r="137">
           <cell r="A137" t="str">
             <v>bpbutor.hu</v>
+          </cell>
+        </row>
+        <row r="138">
+          <cell r="A138" t="str">
+            <v>kormanyhivatal.hu</v>
           </cell>
         </row>
       </sheetData>
@@ -27429,7 +27434,7 @@
       </c>
       <c r="B500" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A500)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.2">

--- a/data/processed/hungarian_websites.xlsx
+++ b/data/processed/hungarian_websites.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A14F6D-BA06-314B-9700-981972499985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB8D7569-54F4-A145-A585-8CCA918B93A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4043,6 +4043,11 @@
         <row r="138">
           <cell r="A138" t="str">
             <v>kormanyhivatal.hu</v>
+          </cell>
+        </row>
+        <row r="139">
+          <cell r="A139" t="str">
+            <v>deninet.hu</v>
           </cell>
         </row>
       </sheetData>
@@ -29504,7 +29509,7 @@
       </c>
       <c r="B730" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A730)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.2">

--- a/data/processed/hungarian_websites.xlsx
+++ b/data/processed/hungarian_websites.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB8D7569-54F4-A145-A585-8CCA918B93A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A53049-BC8A-1D4D-931D-B0FDB9DFB526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4048,6 +4048,11 @@
         <row r="139">
           <cell r="A139" t="str">
             <v>deninet.hu</v>
+          </cell>
+        </row>
+        <row r="140">
+          <cell r="A140" t="str">
+            <v>egy.hu</v>
           </cell>
         </row>
       </sheetData>
@@ -25945,7 +25950,7 @@
       </c>
       <c r="B334" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A334)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.2">

--- a/data/processed/hungarian_websites.xlsx
+++ b/data/processed/hungarian_websites.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A53049-BC8A-1D4D-931D-B0FDB9DFB526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB2AAEE-5953-8544-BAF6-A552DE50D3D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4053,6 +4053,16 @@
         <row r="140">
           <cell r="A140" t="str">
             <v>egy.hu</v>
+          </cell>
+        </row>
+        <row r="141">
+          <cell r="A141" t="str">
+            <v>agraroldal.hu</v>
+          </cell>
+        </row>
+        <row r="142">
+          <cell r="A142" t="str">
+            <v>jatekbolt.hu</v>
           </cell>
         </row>
       </sheetData>
@@ -30315,7 +30325,7 @@
       </c>
       <c r="B819" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A819)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="820" spans="1:2" x14ac:dyDescent="0.2">
@@ -31323,7 +31333,7 @@
       </c>
       <c r="B931" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A931)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="932" spans="1:2" x14ac:dyDescent="0.2">

--- a/data/processed/hungarian_websites.xlsx
+++ b/data/processed/hungarian_websites.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB2AAEE-5953-8544-BAF6-A552DE50D3D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0A13E7-0FA6-2448-8843-5F550E88DD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4063,6 +4063,16 @@
         <row r="142">
           <cell r="A142" t="str">
             <v>jatekbolt.hu</v>
+          </cell>
+        </row>
+        <row r="143">
+          <cell r="A143" t="str">
+            <v>pingvinpatika.hu</v>
+          </cell>
+        </row>
+        <row r="144">
+          <cell r="A144" t="str">
+            <v>termalonline.hu</v>
           </cell>
         </row>
       </sheetData>
@@ -25537,7 +25547,7 @@
       </c>
       <c r="B287" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A287)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.2">
@@ -25663,7 +25673,7 @@
       </c>
       <c r="B301" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A301)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.2">

--- a/data/processed/hungarian_websites.xlsx
+++ b/data/processed/hungarian_websites.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0A13E7-0FA6-2448-8843-5F550E88DD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC6191A-122B-4C4F-B197-851CA1B79759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2160" windowWidth="30680" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hungarian_websites" sheetId="1" r:id="rId1"/>
@@ -4073,6 +4073,11 @@
         <row r="144">
           <cell r="A144" t="str">
             <v>termalonline.hu</v>
+          </cell>
+        </row>
+        <row r="145">
+          <cell r="A145" t="str">
+            <v>laptophardware.hu</v>
           </cell>
         </row>
       </sheetData>
@@ -31163,7 +31168,7 @@
       </c>
       <c r="B911" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A911)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="912" spans="1:2" x14ac:dyDescent="0.2">

--- a/data/processed/hungarian_websites.xlsx
+++ b/data/processed/hungarian_websites.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC6191A-122B-4C4F-B197-851CA1B79759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDDC9DD2-963D-7C48-96D6-7FCD9B5FFBEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="2160" windowWidth="30680" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/processed/hungarian_websites.xlsx
+++ b/data/processed/hungarian_websites.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDDC9DD2-963D-7C48-96D6-7FCD9B5FFBEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5309B2E6-7115-A349-82C8-4266AEA1F2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="2160" windowWidth="30680" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4078,6 +4078,11 @@
         <row r="145">
           <cell r="A145" t="str">
             <v>laptophardware.hu</v>
+          </cell>
+        </row>
+        <row r="146">
+          <cell r="A146" t="str">
+            <v>met.hu</v>
           </cell>
         </row>
       </sheetData>
@@ -27262,7 +27267,7 @@
       </c>
       <c r="B477" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A477)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.2">

--- a/data/processed/hungarian_websites.xlsx
+++ b/data/processed/hungarian_websites.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5309B2E6-7115-A349-82C8-4266AEA1F2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA470E2-3406-264B-BAF0-901AE6C82025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="2160" windowWidth="30680" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4083,6 +4083,11 @@
         <row r="146">
           <cell r="A146" t="str">
             <v>met.hu</v>
+          </cell>
+        </row>
+        <row r="147">
+          <cell r="A147" t="str">
+            <v>studyinhungary.hu</v>
           </cell>
         </row>
       </sheetData>
@@ -29445,7 +29450,7 @@
       </c>
       <c r="B719" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A719)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.2">

--- a/data/processed/hungarian_websites.xlsx
+++ b/data/processed/hungarian_websites.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA470E2-3406-264B-BAF0-901AE6C82025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE7F1983-248D-0442-8020-656BE13D6568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2160" windowWidth="30680" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2660" yWindow="2160" windowWidth="30680" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hungarian_websites" sheetId="1" r:id="rId1"/>
@@ -4088,6 +4088,16 @@
         <row r="147">
           <cell r="A147" t="str">
             <v>studyinhungary.hu</v>
+          </cell>
+        </row>
+        <row r="148">
+          <cell r="A148" t="str">
+            <v>jatekneked.hu</v>
+          </cell>
+        </row>
+        <row r="149">
+          <cell r="A149" t="str">
+            <v>laskod.hu</v>
           </cell>
         </row>
       </sheetData>
@@ -27965,7 +27975,7 @@
       </c>
       <c r="B554" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A554)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.2">
@@ -28343,7 +28353,7 @@
       </c>
       <c r="B596" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A596)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.2">

--- a/data/processed/hungarian_websites.xlsx
+++ b/data/processed/hungarian_websites.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE7F1983-248D-0442-8020-656BE13D6568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A9262E-1737-334A-B46F-3A5FCBB52B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2660" yWindow="2160" windowWidth="30680" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4098,6 +4098,16 @@
         <row r="149">
           <cell r="A149" t="str">
             <v>laskod.hu</v>
+          </cell>
+        </row>
+        <row r="150">
+          <cell r="A150" t="str">
+            <v>mellrakforum.hu</v>
+          </cell>
+        </row>
+        <row r="151">
+          <cell r="A151" t="str">
+            <v>alternativenergia.hu</v>
           </cell>
         </row>
       </sheetData>
@@ -27093,7 +27103,7 @@
       </c>
       <c r="B456" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A456)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.2">
@@ -31530,7 +31540,7 @@
       </c>
       <c r="B949" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A949)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="950" spans="1:2" x14ac:dyDescent="0.2">

--- a/data/processed/hungarian_websites.xlsx
+++ b/data/processed/hungarian_websites.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A9262E-1737-334A-B46F-3A5FCBB52B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54DBA1C2-6B2C-A942-AE24-DF7DB0C0DB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="2160" windowWidth="30680" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1900" yWindow="2180" windowWidth="30680" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hungarian_websites" sheetId="1" r:id="rId1"/>
@@ -4108,6 +4108,16 @@
         <row r="151">
           <cell r="A151" t="str">
             <v>alternativenergia.hu</v>
+          </cell>
+        </row>
+        <row r="152">
+          <cell r="A152" t="str">
+            <v>valtanek.hu</v>
+          </cell>
+        </row>
+        <row r="153">
+          <cell r="A153" t="str">
+            <v>neprajz.hu</v>
           </cell>
         </row>
       </sheetData>
@@ -27904,7 +27914,7 @@
       </c>
       <c r="B545" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A545)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.2">
@@ -29200,7 +29210,7 @@
       </c>
       <c r="B689" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A689)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.2">

--- a/data/processed/hungarian_websites.xlsx
+++ b/data/processed/hungarian_websites.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54DBA1C2-6B2C-A942-AE24-DF7DB0C0DB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76AA5F14-C2F1-2D47-B3BB-C3CE0159F6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="2180" windowWidth="30680" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2080" yWindow="1980" windowWidth="30680" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hungarian_websites" sheetId="1" r:id="rId1"/>
@@ -4118,6 +4118,16 @@
         <row r="153">
           <cell r="A153" t="str">
             <v>neprajz.hu</v>
+          </cell>
+        </row>
+        <row r="154">
+          <cell r="A154" t="str">
+            <v>news7.hu</v>
+          </cell>
+        </row>
+        <row r="155">
+          <cell r="A155" t="str">
+            <v>eblog.hu</v>
           </cell>
         </row>
       </sheetData>
@@ -26582,7 +26592,7 @@
       </c>
       <c r="B397" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A397)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.2">
@@ -27986,7 +27996,7 @@
       </c>
       <c r="B553" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A553)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.2">

--- a/data/processed/hungarian_websites.xlsx
+++ b/data/processed/hungarian_websites.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76AA5F14-C2F1-2D47-B3BB-C3CE0159F6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7045483-6A02-434E-8DAA-5FBEFB5E2F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2080" yWindow="1980" windowWidth="30680" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2500" yWindow="1960" windowWidth="30680" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hungarian_websites" sheetId="1" r:id="rId1"/>
@@ -4128,6 +4128,11 @@
         <row r="155">
           <cell r="A155" t="str">
             <v>eblog.hu</v>
+          </cell>
+        </row>
+        <row r="156">
+          <cell r="A156" t="str">
+            <v>ventil.hu</v>
           </cell>
         </row>
       </sheetData>
@@ -31434,7 +31439,7 @@
       </c>
       <c r="B935" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A935)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="936" spans="1:2" x14ac:dyDescent="0.2">

--- a/data/processed/hungarian_websites.xlsx
+++ b/data/processed/hungarian_websites.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7045483-6A02-434E-8DAA-5FBEFB5E2F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E3595C8-7D6D-7443-ABD1-9DFA8294CF57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2500" yWindow="1960" windowWidth="30680" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2240" yWindow="1800" windowWidth="30680" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hungarian_websites" sheetId="1" r:id="rId1"/>
@@ -4133,6 +4133,11 @@
         <row r="156">
           <cell r="A156" t="str">
             <v>ventil.hu</v>
+          </cell>
+        </row>
+        <row r="157">
+          <cell r="A157" t="str">
+            <v>rtlplusz.hu</v>
           </cell>
         </row>
       </sheetData>
@@ -25508,7 +25513,7 @@
       </c>
       <c r="B276" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A276)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.2">

--- a/data/processed/hungarian_websites.xlsx
+++ b/data/processed/hungarian_websites.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E3595C8-7D6D-7443-ABD1-9DFA8294CF57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9EE5EE6-828C-6545-BBB9-E3180C35129E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2240" yWindow="1800" windowWidth="30680" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4138,6 +4138,11 @@
         <row r="157">
           <cell r="A157" t="str">
             <v>rtlplusz.hu</v>
+          </cell>
+        </row>
+        <row r="158">
+          <cell r="A158" t="str">
+            <v>keptelenseg.hu</v>
           </cell>
         </row>
       </sheetData>
@@ -30346,7 +30351,7 @@
       </c>
       <c r="B813" t="str">
         <f>IF(COUNTIF([1]failed_domains!$A:$A,A813)&gt;0,"Igen","Nem")</f>
-        <v>Nem</v>
+        <v>Igen</v>
       </c>
     </row>
     <row r="814" spans="1:2" x14ac:dyDescent="0.2">
